--- a/data/31August-Tigers-v-Oaks.xlsx
+++ b/data/31August-Tigers-v-Oaks.xlsx
@@ -121,7 +121,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O150"/>
   <sheetData>
     <row r="1">
@@ -680,8 +680,10 @@
       <c r="D64" t="s">
         <v>16</v>
       </c>
-      <c r="E64" t="s">
-        <v>17</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -899,8 +901,10 @@
       <c r="D88" t="s">
         <v>16</v>
       </c>
-      <c r="E88" t="s">
-        <v>17</v>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -988,8 +992,10 @@
       <c r="D98" t="s">
         <v>16</v>
       </c>
-      <c r="E98" t="s">
-        <v>17</v>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -1406,8 +1412,10 @@
       <c r="D145" t="s">
         <v>33</v>
       </c>
-      <c r="E145" t="s">
-        <v>34</v>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
       </c>
     </row>
     <row r="146">
